--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/111.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/111.xlsx
@@ -426,13 +426,13 @@
         <v>-16.76420404391459</v>
       </c>
       <c r="E2">
-        <v>-7.347428511782718</v>
+        <v>-8.364650571177696</v>
       </c>
       <c r="F2">
-        <v>-3.92492752196939</v>
+        <v>-4.921692228823035</v>
       </c>
       <c r="G2">
-        <v>-10.45858392305877</v>
+        <v>-11.86190431388259</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.00173226864981</v>
       </c>
       <c r="E3">
-        <v>-7.124165686256554</v>
+        <v>-10.47324392336924</v>
       </c>
       <c r="F3">
-        <v>-4.08229958693365</v>
+        <v>-4.381649303511141</v>
       </c>
       <c r="G3">
-        <v>-12.01812564733526</v>
+        <v>-11.69932011190344</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.15174533322321</v>
       </c>
       <c r="E4">
-        <v>-8.264698092880396</v>
+        <v>-11.08443847476249</v>
       </c>
       <c r="F4">
-        <v>-4.363144491742189</v>
+        <v>-4.306361507997066</v>
       </c>
       <c r="G4">
-        <v>-10.30392847764618</v>
+        <v>-11.96108163714807</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.29921332049596</v>
       </c>
       <c r="E5">
-        <v>-8.103534231421415</v>
+        <v>-12.66991609500998</v>
       </c>
       <c r="F5">
-        <v>-4.043307955442573</v>
+        <v>-4.001496535569056</v>
       </c>
       <c r="G5">
-        <v>-11.16379302328878</v>
+        <v>-11.47289203919945</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.41429614413214</v>
       </c>
       <c r="E6">
-        <v>-9.174214926476941</v>
+        <v>-10.90250250303033</v>
       </c>
       <c r="F6">
-        <v>-4.102122833877206</v>
+        <v>-4.277568942601419</v>
       </c>
       <c r="G6">
-        <v>-11.1219742120367</v>
+        <v>-11.75940651344121</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.51102049221376</v>
       </c>
       <c r="E7">
-        <v>-10.25284762188994</v>
+        <v>-13.19528700700986</v>
       </c>
       <c r="F7">
-        <v>-3.927687921380001</v>
+        <v>-4.314446326695384</v>
       </c>
       <c r="G7">
-        <v>-11.96636857837429</v>
+        <v>-10.91822668682226</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.56495728102371</v>
       </c>
       <c r="E8">
-        <v>-10.56256354469653</v>
+        <v>-14.56171781103233</v>
       </c>
       <c r="F8">
-        <v>-4.002503772531275</v>
+        <v>-4.394745759578868</v>
       </c>
       <c r="G8">
-        <v>-11.45017507570897</v>
+        <v>-11.41600693519815</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.58449622933442</v>
       </c>
       <c r="E9">
-        <v>-11.93021703670107</v>
+        <v>-14.6232778866926</v>
       </c>
       <c r="F9">
-        <v>-3.991189777471376</v>
+        <v>-4.147948156393404</v>
       </c>
       <c r="G9">
-        <v>-11.90968210710535</v>
+        <v>-11.24087245507963</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.563034214309139</v>
       </c>
       <c r="E10">
-        <v>-13.70645209604767</v>
+        <v>-15.07434106870061</v>
       </c>
       <c r="F10">
-        <v>-3.767217335792183</v>
+        <v>-3.618552485951009</v>
       </c>
       <c r="G10">
-        <v>-10.31744212453748</v>
+        <v>-10.89520515314217</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.506129426127181</v>
       </c>
       <c r="E11">
-        <v>-13.28889509322241</v>
+        <v>-16.82509893328006</v>
       </c>
       <c r="F11">
-        <v>-3.484028546228794</v>
+        <v>-3.794970990107302</v>
       </c>
       <c r="G11">
-        <v>-10.96353812361826</v>
+        <v>-10.94134091577745</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.434716687810131</v>
       </c>
       <c r="E12">
-        <v>-14.31810402331569</v>
+        <v>-17.05588808260697</v>
       </c>
       <c r="F12">
-        <v>-3.786261399425343</v>
+        <v>-3.667599858152169</v>
       </c>
       <c r="G12">
-        <v>-10.45503832878621</v>
+        <v>-10.80473125409942</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.361937403957231</v>
       </c>
       <c r="E13">
-        <v>-15.37396755141812</v>
+        <v>-17.71296513264593</v>
       </c>
       <c r="F13">
-        <v>-3.692051485633596</v>
+        <v>-3.481885792125204</v>
       </c>
       <c r="G13">
-        <v>-9.860292201565061</v>
+        <v>-10.10374640997752</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.327355374153975</v>
       </c>
       <c r="E14">
-        <v>-16.82050706063628</v>
+        <v>-19.38171686142047</v>
       </c>
       <c r="F14">
-        <v>-3.997795414844674</v>
+        <v>-3.952551312399442</v>
       </c>
       <c r="G14">
-        <v>-9.676878047052821</v>
+        <v>-7.898237797896286</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.358899040489804</v>
       </c>
       <c r="E15">
-        <v>-17.36713462962816</v>
+        <v>-19.21984202954228</v>
       </c>
       <c r="F15">
-        <v>-3.798497111328028</v>
+        <v>-3.875426418023457</v>
       </c>
       <c r="G15">
-        <v>-8.822902961924582</v>
+        <v>-8.330267301316715</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.485901193174139</v>
       </c>
       <c r="E16">
-        <v>-18.29936176037317</v>
+        <v>-19.55494004916188</v>
       </c>
       <c r="F16">
-        <v>-3.838776295728357</v>
+        <v>-3.505319096703004</v>
       </c>
       <c r="G16">
-        <v>-7.86405972574885</v>
+        <v>-8.18034262547974</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.736863867524669</v>
       </c>
       <c r="E17">
-        <v>-18.68842560474217</v>
+        <v>-20.88126668737242</v>
       </c>
       <c r="F17">
-        <v>-3.669493970427034</v>
+        <v>-3.444496871020552</v>
       </c>
       <c r="G17">
-        <v>-6.708050328890744</v>
+        <v>-6.728780965057661</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.119388811306304</v>
       </c>
       <c r="E18">
-        <v>-20.26292620399507</v>
+        <v>-21.74795321380442</v>
       </c>
       <c r="F18">
-        <v>-3.579967075027243</v>
+        <v>-3.375393447106267</v>
       </c>
       <c r="G18">
-        <v>-6.43597976483682</v>
+        <v>-6.075189890875968</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.649266927281065</v>
       </c>
       <c r="E19">
-        <v>-20.04696327856927</v>
+        <v>-21.21318118976462</v>
       </c>
       <c r="F19">
-        <v>-3.264372495022131</v>
+        <v>-2.95046218625809</v>
       </c>
       <c r="G19">
-        <v>-6.52760242318169</v>
+        <v>-6.105686636383734</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.322978443325977</v>
       </c>
       <c r="E20">
-        <v>-22.69707608107205</v>
+        <v>-23.92376270569182</v>
       </c>
       <c r="F20">
-        <v>-2.872961161727187</v>
+        <v>-3.316704473291912</v>
       </c>
       <c r="G20">
-        <v>-5.102180830337694</v>
+        <v>-5.935663638577845</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.142658368196895</v>
       </c>
       <c r="E21">
-        <v>-22.89499303757728</v>
+        <v>-24.79657625745619</v>
       </c>
       <c r="F21">
-        <v>-3.115707645180957</v>
+        <v>-2.430514113454249</v>
       </c>
       <c r="G21">
-        <v>-3.763730579355893</v>
+        <v>-5.564359471984266</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.108617652707897</v>
       </c>
       <c r="E22">
-        <v>-22.85535077611413</v>
+        <v>-26.83368311896266</v>
       </c>
       <c r="F22">
-        <v>-2.409492792985664</v>
+        <v>-2.795780045791203</v>
       </c>
       <c r="G22">
-        <v>-5.02684605604604</v>
+        <v>-5.635287910163152</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.214156443306465</v>
       </c>
       <c r="E23">
-        <v>-23.60443283256693</v>
+        <v>-25.97893817848889</v>
       </c>
       <c r="F23">
-        <v>-2.688872769822421</v>
+        <v>-1.984708024934664</v>
       </c>
       <c r="G23">
-        <v>-4.356242088338032</v>
+        <v>-5.973466758090782</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.456108876807821</v>
       </c>
       <c r="E24">
-        <v>-24.6899533369456</v>
+        <v>-25.85924608199215</v>
       </c>
       <c r="F24">
-        <v>-2.490036116580125</v>
+        <v>-2.332938032739236</v>
       </c>
       <c r="G24">
-        <v>-3.964485371402837</v>
+        <v>-5.159297672526741</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.81251757647707</v>
       </c>
       <c r="E25">
-        <v>-24.30015135131335</v>
+        <v>-27.22677277672448</v>
       </c>
       <c r="F25">
-        <v>-2.303130311851793</v>
+        <v>-2.352000308990423</v>
       </c>
       <c r="G25">
-        <v>-3.567289428146619</v>
+        <v>-5.235764653392827</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.259799150116199</v>
       </c>
       <c r="E26">
-        <v>-25.05561402764295</v>
+        <v>-26.95408165740459</v>
       </c>
       <c r="F26">
-        <v>-2.121049267194846</v>
+        <v>-1.471663326216224</v>
       </c>
       <c r="G26">
-        <v>-5.308573481438017</v>
+        <v>-5.360098812211234</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.760053837336592</v>
       </c>
       <c r="E27">
-        <v>-25.70562212975594</v>
+        <v>-27.74199537847316</v>
       </c>
       <c r="F27">
-        <v>-2.417449331504832</v>
+        <v>-1.624741172590771</v>
       </c>
       <c r="G27">
-        <v>-4.9121025476549</v>
+        <v>-5.445150037660651</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.270087738941953</v>
       </c>
       <c r="E28">
-        <v>-25.93557803986544</v>
+        <v>-27.82501589245578</v>
       </c>
       <c r="F28">
-        <v>-2.207312144702918</v>
+        <v>-1.956851429735042</v>
       </c>
       <c r="G28">
-        <v>-4.728651977141727</v>
+        <v>-5.552928158237163</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.746651294819243</v>
       </c>
       <c r="E29">
-        <v>-24.72280741587124</v>
+        <v>-28.49296128011315</v>
       </c>
       <c r="F29">
-        <v>-1.842720871085941</v>
+        <v>-1.590983689150221</v>
       </c>
       <c r="G29">
-        <v>-4.738821973038368</v>
+        <v>-6.685624693407721</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.145848103972869</v>
       </c>
       <c r="E30">
-        <v>-24.76497203735666</v>
+        <v>-26.40905716821142</v>
       </c>
       <c r="F30">
-        <v>-2.37630623552763</v>
+        <v>-2.209235555537219</v>
       </c>
       <c r="G30">
-        <v>-5.438095265116464</v>
+        <v>-6.321272672446613</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.434016585055479</v>
       </c>
       <c r="E31">
-        <v>-25.42878745671904</v>
+        <v>-26.98813578194227</v>
       </c>
       <c r="F31">
-        <v>-2.026337318627906</v>
+        <v>-1.941615386975557</v>
       </c>
       <c r="G31">
-        <v>-5.582024542981817</v>
+        <v>-5.852592119360913</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.585684067036656</v>
       </c>
       <c r="E32">
-        <v>-24.75701098005118</v>
+        <v>-27.73425168792005</v>
       </c>
       <c r="F32">
-        <v>-1.677265571129278</v>
+        <v>-1.748407224556733</v>
       </c>
       <c r="G32">
-        <v>-6.016550197738857</v>
+        <v>-7.043987937488288</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.589091151685365</v>
       </c>
       <c r="E33">
-        <v>-24.39821998442346</v>
+        <v>-24.7494076721923</v>
       </c>
       <c r="F33">
-        <v>-2.115743852378124</v>
+        <v>-1.939993672118147</v>
       </c>
       <c r="G33">
-        <v>-6.285800176993322</v>
+        <v>-6.673809356378062</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.446171094049499</v>
       </c>
       <c r="E34">
-        <v>-23.43684759496508</v>
+        <v>-27.93013535959583</v>
       </c>
       <c r="F34">
-        <v>-2.175523999568217</v>
+        <v>-2.31038922791521</v>
       </c>
       <c r="G34">
-        <v>-5.258590864886101</v>
+        <v>-7.742973212104467</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.169399646055783</v>
       </c>
       <c r="E35">
-        <v>-23.91428460959376</v>
+        <v>-24.97947679415199</v>
       </c>
       <c r="F35">
-        <v>-1.746734039257071</v>
+        <v>-2.367256148073852</v>
       </c>
       <c r="G35">
-        <v>-5.584775606324952</v>
+        <v>-5.906206404369409</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.784262746068968</v>
       </c>
       <c r="E36">
-        <v>-23.18947970229608</v>
+        <v>-25.13508874647757</v>
       </c>
       <c r="F36">
-        <v>-1.988059146651734</v>
+        <v>-2.007572779088822</v>
       </c>
       <c r="G36">
-        <v>-6.200477486809686</v>
+        <v>-6.853535563159556</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.324388988446852</v>
       </c>
       <c r="E37">
-        <v>-22.43989045675442</v>
+        <v>-26.45353131144076</v>
       </c>
       <c r="F37">
-        <v>-1.837379031033163</v>
+        <v>-2.030490587391145</v>
       </c>
       <c r="G37">
-        <v>-5.87822236292595</v>
+        <v>-4.948813187139878</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.829402636733371</v>
       </c>
       <c r="E38">
-        <v>-21.84112656651223</v>
+        <v>-25.795394598484</v>
       </c>
       <c r="F38">
-        <v>-2.322759554820707</v>
+        <v>-2.305897046086065</v>
       </c>
       <c r="G38">
-        <v>-6.819436944105063</v>
+        <v>-5.522060631628999</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.342921528204884</v>
       </c>
       <c r="E39">
-        <v>-22.68987127892584</v>
+        <v>-25.67219293463132</v>
       </c>
       <c r="F39">
-        <v>-1.97427773777558</v>
+        <v>-2.003294397558262</v>
       </c>
       <c r="G39">
-        <v>-6.765269797991508</v>
+        <v>-6.172288191542791</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.900723718949729</v>
       </c>
       <c r="E40">
-        <v>-21.87985860469984</v>
+        <v>-23.22530446017076</v>
       </c>
       <c r="F40">
-        <v>-1.80353602747318</v>
+        <v>-1.949744549439508</v>
       </c>
       <c r="G40">
-        <v>-7.030510706597915</v>
+        <v>-5.893046985850806</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.535828670936875</v>
       </c>
       <c r="E41">
-        <v>-21.9604835559324</v>
+        <v>-22.46086634835795</v>
       </c>
       <c r="F41">
-        <v>-2.311956304918537</v>
+        <v>-2.39735368714382</v>
       </c>
       <c r="G41">
-        <v>-7.006575462348985</v>
+        <v>-5.358423676168363</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.267546568743356</v>
       </c>
       <c r="E42">
-        <v>-20.84928207545624</v>
+        <v>-23.68351810263689</v>
       </c>
       <c r="F42">
-        <v>-2.54652373917202</v>
+        <v>-2.417431118886804</v>
       </c>
       <c r="G42">
-        <v>-5.778419346553542</v>
+        <v>-5.334183861729819</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.105279120337159</v>
       </c>
       <c r="E43">
-        <v>-19.43499435812071</v>
+        <v>-23.18785398012733</v>
       </c>
       <c r="F43">
-        <v>-2.185260623536339</v>
+        <v>-2.818087335463126</v>
       </c>
       <c r="G43">
-        <v>-5.986202426780358</v>
+        <v>-5.635076035248638</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.050118294777836</v>
       </c>
       <c r="E44">
-        <v>-18.3131962484666</v>
+        <v>-22.55179810643197</v>
       </c>
       <c r="F44">
-        <v>-2.203001297201091</v>
+        <v>-2.483694958094706</v>
       </c>
       <c r="G44">
-        <v>-6.217060009415896</v>
+        <v>-6.070806728581973</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.088122400079499</v>
       </c>
       <c r="E45">
-        <v>-19.89014222368365</v>
+        <v>-21.7561497517583</v>
       </c>
       <c r="F45">
-        <v>-2.052161227285061</v>
+        <v>-2.604892012538498</v>
       </c>
       <c r="G45">
-        <v>-4.957238525537323</v>
+        <v>-5.13154867981657</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.205564477315433</v>
       </c>
       <c r="E46">
-        <v>-18.1537305647605</v>
+        <v>-20.21916755965895</v>
       </c>
       <c r="F46">
-        <v>-2.139222292574514</v>
+        <v>-2.549803594122895</v>
       </c>
       <c r="G46">
-        <v>-5.99973262639936</v>
+        <v>-5.157894001218089</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.377851622702406</v>
       </c>
       <c r="E47">
-        <v>-18.14082894231265</v>
+        <v>-21.39268537095466</v>
       </c>
       <c r="F47">
-        <v>-2.378441071101642</v>
+        <v>-2.984680528120032</v>
       </c>
       <c r="G47">
-        <v>-6.111298011072798</v>
+        <v>-5.065215278846193</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.584542877822106</v>
       </c>
       <c r="E48">
-        <v>-17.07714473959897</v>
+        <v>-20.16404244556358</v>
       </c>
       <c r="F48">
-        <v>-2.33448214600679</v>
+        <v>-2.835935701130128</v>
       </c>
       <c r="G48">
-        <v>-6.386725468303544</v>
+        <v>-5.633622705756898</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.807872419173652</v>
       </c>
       <c r="E49">
-        <v>-15.84616059314592</v>
+        <v>-18.77013738973658</v>
       </c>
       <c r="F49">
-        <v>-1.998270882394488</v>
+        <v>-2.510188774354093</v>
       </c>
       <c r="G49">
-        <v>-5.050092706822801</v>
+        <v>-4.462242445959957</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.034913616396295</v>
       </c>
       <c r="E50">
-        <v>-17.30039397970311</v>
+        <v>-18.21006025294191</v>
       </c>
       <c r="F50">
-        <v>-2.425270463168229</v>
+        <v>-2.363929573798471</v>
       </c>
       <c r="G50">
-        <v>-6.012978119101984</v>
+        <v>-5.635129003977267</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.265813323724064</v>
       </c>
       <c r="E51">
-        <v>-15.85295783263144</v>
+        <v>-19.36704913410963</v>
       </c>
       <c r="F51">
-        <v>-2.078966241756832</v>
+        <v>-2.624752476571067</v>
       </c>
       <c r="G51">
-        <v>-6.512734763164823</v>
+        <v>-5.064212183547793</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.501093133793133</v>
       </c>
       <c r="E52">
-        <v>-14.99849365754614</v>
+        <v>-19.18251381829706</v>
       </c>
       <c r="F52">
-        <v>-2.649923106538103</v>
+        <v>-3.006945849585196</v>
       </c>
       <c r="G52">
-        <v>-5.775568966844229</v>
+        <v>-5.329512681973908</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.752437013588472</v>
       </c>
       <c r="E53">
-        <v>-13.67522826776479</v>
+        <v>-17.2754103886028</v>
       </c>
       <c r="F53">
-        <v>-2.238051876521598</v>
+        <v>-2.857423422990811</v>
       </c>
       <c r="G53">
-        <v>-5.703114367171739</v>
+        <v>-4.436804214036196</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.02782724395144</v>
       </c>
       <c r="E54">
-        <v>-13.75163720969621</v>
+        <v>-17.42477757527179</v>
       </c>
       <c r="F54">
-        <v>-2.280606054469455</v>
+        <v>-2.464236755364659</v>
       </c>
       <c r="G54">
-        <v>-6.765842522369802</v>
+        <v>-5.723543743694583</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.334694560290741</v>
       </c>
       <c r="E55">
-        <v>-13.72550791467195</v>
+        <v>-17.37736898088549</v>
       </c>
       <c r="F55">
-        <v>-2.066270463285711</v>
+        <v>-2.788441944432015</v>
       </c>
       <c r="G55">
-        <v>-5.328307643397613</v>
+        <v>-5.133793229692195</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.679523687659752</v>
       </c>
       <c r="E56">
-        <v>-11.38877457044797</v>
+        <v>-14.91276058763293</v>
       </c>
       <c r="F56">
-        <v>-2.162176526112893</v>
+        <v>-3.142498406299489</v>
       </c>
       <c r="G56">
-        <v>-5.441564716841619</v>
+        <v>-4.760247823768531</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.057365398628076</v>
       </c>
       <c r="E57">
-        <v>-12.28790761314493</v>
+        <v>-15.6203255943834</v>
       </c>
       <c r="F57">
-        <v>-2.405742577377903</v>
+        <v>-3.152482880243376</v>
       </c>
       <c r="G57">
-        <v>-5.926602675436859</v>
+        <v>-4.763392842030838</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.469569566658527</v>
       </c>
       <c r="E58">
-        <v>-12.11635996078636</v>
+        <v>-13.54670111847908</v>
       </c>
       <c r="F58">
-        <v>-2.667170455810197</v>
+        <v>-3.029208795491485</v>
       </c>
       <c r="G58">
-        <v>-6.473494866887841</v>
+        <v>-6.138970861235567</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.906928334272791</v>
       </c>
       <c r="E59">
-        <v>-11.52089279962176</v>
+        <v>-15.64352949519871</v>
       </c>
       <c r="F59">
-        <v>-2.333261108745986</v>
+        <v>-3.205808633975096</v>
       </c>
       <c r="G59">
-        <v>-6.165504883732825</v>
+        <v>-6.225971998007613</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.361293845828541</v>
       </c>
       <c r="E60">
-        <v>-11.25461399949673</v>
+        <v>-15.03277873425821</v>
       </c>
       <c r="F60">
-        <v>-2.600107636967956</v>
+        <v>-3.298159277022116</v>
       </c>
       <c r="G60">
-        <v>-6.730813640018773</v>
+        <v>-4.907298946077418</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.824719016907632</v>
       </c>
       <c r="E61">
-        <v>-9.845959703826747</v>
+        <v>-14.77025403908555</v>
       </c>
       <c r="F61">
-        <v>-3.140092757013936</v>
+        <v>-3.545152467888137</v>
       </c>
       <c r="G61">
-        <v>-7.089147089189487</v>
+        <v>-6.564011803022594</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.280671408778685</v>
       </c>
       <c r="E62">
-        <v>-9.465490903124305</v>
+        <v>-13.19703046950281</v>
       </c>
       <c r="F62">
-        <v>-2.428608123385018</v>
+        <v>-2.931314389887469</v>
       </c>
       <c r="G62">
-        <v>-6.560062322194244</v>
+        <v>-6.422188032120217</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.720121240281491</v>
       </c>
       <c r="E63">
-        <v>-10.23308988979447</v>
+        <v>-13.55194509137997</v>
       </c>
       <c r="F63">
-        <v>-2.534319701387644</v>
+        <v>-3.330017105217096</v>
       </c>
       <c r="G63">
-        <v>-6.615023999237224</v>
+        <v>-7.403460214324511</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.124184553005959</v>
       </c>
       <c r="E64">
-        <v>-8.448640178597957</v>
+        <v>-12.04257753377939</v>
       </c>
       <c r="F64">
-        <v>-2.429632781112307</v>
+        <v>-3.580477820184972</v>
       </c>
       <c r="G64">
-        <v>-7.41327267130291</v>
+        <v>-6.528638623935482</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.475265655385154</v>
       </c>
       <c r="E65">
-        <v>-8.859513153787898</v>
+        <v>-12.29149869303301</v>
       </c>
       <c r="F65">
-        <v>-2.608300147668524</v>
+        <v>-3.742677020779491</v>
       </c>
       <c r="G65">
-        <v>-7.279579600244983</v>
+        <v>-8.006111924293437</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.756136472223074</v>
       </c>
       <c r="E66">
-        <v>-8.156390580038943</v>
+        <v>-12.62016175108771</v>
       </c>
       <c r="F66">
-        <v>-2.913097020742169</v>
+        <v>-3.754272915492339</v>
       </c>
       <c r="G66">
-        <v>-8.002533224565486</v>
+        <v>-7.216394528082453</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.945611388197241</v>
       </c>
       <c r="E67">
-        <v>-8.799279921011873</v>
+        <v>-11.19896358241647</v>
       </c>
       <c r="F67">
-        <v>-3.152681635335764</v>
+        <v>-3.404858295663018</v>
       </c>
       <c r="G67">
-        <v>-9.111003187479657</v>
+        <v>-7.955722110640191</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.031915903764816</v>
       </c>
       <c r="E68">
-        <v>-8.672491705745118</v>
+        <v>-11.78463565430249</v>
       </c>
       <c r="F68">
-        <v>-2.912035937778825</v>
+        <v>-3.750219420201772</v>
       </c>
       <c r="G68">
-        <v>-8.985096519530096</v>
+        <v>-8.104954882459458</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.001922729029937</v>
       </c>
       <c r="E69">
-        <v>-9.274529682694855</v>
+        <v>-12.47828013195339</v>
       </c>
       <c r="F69">
-        <v>-2.581230654308875</v>
+        <v>-3.878978670391787</v>
       </c>
       <c r="G69">
-        <v>-8.402632516259644</v>
+        <v>-8.016089908548802</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.848907945764424</v>
       </c>
       <c r="E70">
-        <v>-8.087344936843994</v>
+        <v>-9.825749124330514</v>
       </c>
       <c r="F70">
-        <v>-3.141113455476437</v>
+        <v>-3.733990393833306</v>
       </c>
       <c r="G70">
-        <v>-8.877616348052117</v>
+        <v>-7.861954218785874</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.575104230579985</v>
       </c>
       <c r="E71">
-        <v>-9.216814281467096</v>
+        <v>-10.18666850274184</v>
       </c>
       <c r="F71">
-        <v>-3.615748534627724</v>
+        <v>-3.644224358840283</v>
       </c>
       <c r="G71">
-        <v>-8.824223869594752</v>
+        <v>-8.782299120885421</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.184045936331069</v>
       </c>
       <c r="E72">
-        <v>-8.572181478001212</v>
+        <v>-13.25369073628678</v>
       </c>
       <c r="F72">
-        <v>-3.58699318632109</v>
+        <v>-4.372642767970037</v>
       </c>
       <c r="G72">
-        <v>-9.266893466378399</v>
+        <v>-8.346747197011206</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.692797656297981</v>
       </c>
       <c r="E73">
-        <v>-8.782338899749179</v>
+        <v>-12.41025339541016</v>
       </c>
       <c r="F73">
-        <v>-3.714278006303831</v>
+        <v>-3.856942986284363</v>
       </c>
       <c r="G73">
-        <v>-8.124222257498015</v>
+        <v>-8.784752235130021</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.120847604984849</v>
       </c>
       <c r="E74">
-        <v>-8.52073348480007</v>
+        <v>-11.5582889379771</v>
       </c>
       <c r="F74">
-        <v>-3.870271455268701</v>
+        <v>-3.701459490624264</v>
       </c>
       <c r="G74">
-        <v>-8.728645109330452</v>
+        <v>-7.969325142261056</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.491363002474006</v>
       </c>
       <c r="E75">
-        <v>-8.011574509747653</v>
+        <v>-12.86315060939128</v>
       </c>
       <c r="F75">
-        <v>-3.402342578816343</v>
+        <v>-4.287450475660803</v>
       </c>
       <c r="G75">
-        <v>-8.30321683371533</v>
+        <v>-7.58824493469001</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.833989555523915</v>
       </c>
       <c r="E76">
-        <v>-8.405456650460813</v>
+        <v>-13.44900834871161</v>
       </c>
       <c r="F76">
-        <v>-3.932636210512791</v>
+        <v>-4.289604315705801</v>
       </c>
       <c r="G76">
-        <v>-9.043348878839112</v>
+        <v>-7.631070151786022</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.170311392137434</v>
       </c>
       <c r="E77">
-        <v>-8.678369665007075</v>
+        <v>-13.40966043805896</v>
       </c>
       <c r="F77">
-        <v>-4.344171694875224</v>
+        <v>-4.204444489367833</v>
       </c>
       <c r="G77">
-        <v>-7.974112191110843</v>
+        <v>-7.761115001659673</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.529806216917935</v>
       </c>
       <c r="E78">
-        <v>-10.97918768187622</v>
+        <v>-12.54981643585256</v>
       </c>
       <c r="F78">
-        <v>-3.96806450369413</v>
+        <v>-4.872537956472583</v>
       </c>
       <c r="G78">
-        <v>-8.058938299463588</v>
+        <v>-7.851857054891097</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.933141159620814</v>
       </c>
       <c r="E79">
-        <v>-10.44084722031837</v>
+        <v>-13.5238051538963</v>
       </c>
       <c r="F79">
-        <v>-4.368665290563411</v>
+        <v>-4.586230849961694</v>
       </c>
       <c r="G79">
-        <v>-8.575042417399349</v>
+        <v>-7.657581000464506</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.396566855921848</v>
       </c>
       <c r="E80">
-        <v>-10.76139072447731</v>
+        <v>-14.99780532949698</v>
       </c>
       <c r="F80">
-        <v>-4.343878709280868</v>
+        <v>-4.90086174491726</v>
       </c>
       <c r="G80">
-        <v>-8.124804913512927</v>
+        <v>-7.060219542267335</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.935060995278753</v>
       </c>
       <c r="E81">
-        <v>-12.13536143772255</v>
+        <v>-15.16947072217974</v>
       </c>
       <c r="F81">
-        <v>-4.402281032324528</v>
+        <v>-4.985554378010173</v>
       </c>
       <c r="G81">
-        <v>-7.826220190234981</v>
+        <v>-7.214116872751434</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.549410917225271</v>
       </c>
       <c r="E82">
-        <v>-12.13880760644239</v>
+        <v>-15.35152896271011</v>
       </c>
       <c r="F82">
-        <v>-4.457286306179571</v>
+        <v>-5.106862291868046</v>
       </c>
       <c r="G82">
-        <v>-7.083522472318265</v>
+        <v>-7.161701005228154</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.246139259065475</v>
       </c>
       <c r="E83">
-        <v>-14.0243328574901</v>
+        <v>-16.80722051789777</v>
       </c>
       <c r="F83">
-        <v>-4.535256899514402</v>
+        <v>-5.070618390140257</v>
       </c>
       <c r="G83">
-        <v>-7.944558951081769</v>
+        <v>-7.110354443914058</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.020472759039372</v>
       </c>
       <c r="E84">
-        <v>-14.75329943240083</v>
+        <v>-16.28109335073862</v>
       </c>
       <c r="F84">
-        <v>-4.759457394845418</v>
+        <v>-4.748675524973106</v>
       </c>
       <c r="G84">
-        <v>-7.242524664023921</v>
+        <v>-7.353795410144365</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.8717810977684877</v>
       </c>
       <c r="E85">
-        <v>-14.46229516419392</v>
+        <v>-17.28146042987704</v>
       </c>
       <c r="F85">
-        <v>-4.586212637343666</v>
+        <v>-4.881895282873957</v>
       </c>
       <c r="G85">
-        <v>-8.048715334838318</v>
+        <v>-6.550256486306923</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.8004886080629272</v>
       </c>
       <c r="E86">
-        <v>-15.11319990416043</v>
+        <v>-17.850567343843</v>
       </c>
       <c r="F86">
-        <v>-4.639150383126102</v>
+        <v>-5.071918612696832</v>
       </c>
       <c r="G86">
-        <v>-7.532425826352359</v>
+        <v>-6.994290027852749</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.8050874098453425</v>
       </c>
       <c r="E87">
-        <v>-17.53064424062311</v>
+        <v>-20.64222665840353</v>
       </c>
       <c r="F87">
-        <v>-5.161746412220558</v>
+        <v>-5.112307072805327</v>
       </c>
       <c r="G87">
-        <v>-7.53873241560467</v>
+        <v>-6.561072038583721</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.8936862472996503</v>
       </c>
       <c r="E88">
-        <v>-19.70639939082242</v>
+        <v>-21.78760453221558</v>
       </c>
       <c r="F88">
-        <v>-4.874743266959833</v>
+        <v>-5.184859016350481</v>
       </c>
       <c r="G88">
-        <v>-8.032195712597355</v>
+        <v>-7.441405687295637</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.066406284927574</v>
       </c>
       <c r="E89">
-        <v>-20.28128916609617</v>
+        <v>-23.22602448753798</v>
       </c>
       <c r="F89">
-        <v>-5.327326033091583</v>
+        <v>-5.385105167857518</v>
       </c>
       <c r="G89">
-        <v>-7.097449937401978</v>
+        <v>-7.001265347303994</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.333931132686508</v>
       </c>
       <c r="E90">
-        <v>-20.86150895527695</v>
+        <v>-23.43486412334972</v>
       </c>
       <c r="F90">
-        <v>-5.394542471407622</v>
+        <v>-5.114168719108926</v>
       </c>
       <c r="G90">
-        <v>-7.445878234319192</v>
+        <v>-7.217844547028654</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.69934376316999</v>
       </c>
       <c r="E91">
-        <v>-24.11868634087798</v>
+        <v>-27.31119258917547</v>
       </c>
       <c r="F91">
-        <v>-5.070209794014073</v>
+        <v>-5.05854659179982</v>
       </c>
       <c r="G91">
-        <v>-7.864400711939395</v>
+        <v>-6.493308481940379</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.166032636672701</v>
       </c>
       <c r="E92">
-        <v>-25.32953689189292</v>
+        <v>-29.93540704882838</v>
       </c>
       <c r="F92">
-        <v>-5.278585899838019</v>
+        <v>-6.084670038913881</v>
       </c>
       <c r="G92">
-        <v>-7.785156183365861</v>
+        <v>-6.960006018248056</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.737415332614905</v>
       </c>
       <c r="E93">
-        <v>-26.73541523299621</v>
+        <v>-30.40066926108744</v>
       </c>
       <c r="F93">
-        <v>-5.563045613398548</v>
+        <v>-5.520333856712104</v>
       </c>
       <c r="G93">
-        <v>-7.783100334585973</v>
+        <v>-7.347948986722011</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.403025306469363</v>
       </c>
       <c r="E94">
-        <v>-28.73066540924978</v>
+        <v>-31.407611684485</v>
       </c>
       <c r="F94">
-        <v>-5.112984107084177</v>
+        <v>-5.185868628871574</v>
       </c>
       <c r="G94">
-        <v>-8.160558805337056</v>
+        <v>-7.58170329670441</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.158070029748703</v>
       </c>
       <c r="E95">
-        <v>-31.07246158741433</v>
+        <v>-34.7447075793734</v>
       </c>
       <c r="F95">
-        <v>-5.200622433179808</v>
+        <v>-5.204896063592621</v>
       </c>
       <c r="G95">
-        <v>-7.691186348233648</v>
+        <v>-7.649754870809669</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.989804803813297</v>
       </c>
       <c r="E96">
-        <v>-33.63480577093744</v>
+        <v>-37.64416042497551</v>
       </c>
       <c r="F96">
-        <v>-4.874550054838149</v>
+        <v>-5.166106354605763</v>
       </c>
       <c r="G96">
-        <v>-8.402851012265236</v>
+        <v>-7.712645304419204</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.871866038345399</v>
       </c>
       <c r="E97">
-        <v>-35.18825123029168</v>
+        <v>-39.28611943728367</v>
       </c>
       <c r="F97">
-        <v>-4.796189077995163</v>
+        <v>-5.034850392040057</v>
       </c>
       <c r="G97">
-        <v>-8.129853495460315</v>
+        <v>-8.281784361894088</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.803784124828276</v>
       </c>
       <c r="E98">
-        <v>-37.77212377924726</v>
+        <v>-39.56323487570905</v>
       </c>
       <c r="F98">
-        <v>-4.756983646205502</v>
+        <v>-5.016047843559002</v>
       </c>
       <c r="G98">
-        <v>-8.197113849181688</v>
+        <v>-8.611445176149173</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.728943248067573</v>
       </c>
       <c r="E99">
-        <v>-38.26601273994581</v>
+        <v>-42.48628559936513</v>
       </c>
       <c r="F99">
-        <v>-4.601291893217523</v>
+        <v>-4.433406396533618</v>
       </c>
       <c r="G99">
-        <v>-8.744373511187529</v>
+        <v>-9.269032078796767</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.674715125532167</v>
       </c>
       <c r="E100">
-        <v>-41.9628324961075</v>
+        <v>-45.26814982464708</v>
       </c>
       <c r="F100">
-        <v>-4.616205651823216</v>
+        <v>-4.322437706744691</v>
       </c>
       <c r="G100">
-        <v>-8.945998976711302</v>
+        <v>-7.489696615076986</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.537451190728337</v>
       </c>
       <c r="E101">
-        <v>-43.86258394825032</v>
+        <v>-47.49934481788529</v>
       </c>
       <c r="F101">
-        <v>-4.738315712727259</v>
+        <v>-4.221439237546414</v>
       </c>
       <c r="G101">
-        <v>-8.00392034314644</v>
+        <v>-8.195322844044943</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.41719620403809</v>
       </c>
       <c r="E102">
-        <v>-46.60193485954824</v>
+        <v>-50.152371693412</v>
       </c>
       <c r="F102">
-        <v>-3.74924068994603</v>
+        <v>-3.747752798238475</v>
       </c>
       <c r="G102">
-        <v>-10.1929755438975</v>
+        <v>-8.544525808618346</v>
       </c>
     </row>
   </sheetData>
